--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-examination-report.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-examination-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Examination Report</t>
+    <t>Logical model - FR LM Examination Report</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -397,16 +397,6 @@
     <t>Conditions ou observations associées aux conclusions</t>
   </si>
   <si>
-    <t>fr-lm-examination-report.subSection.recommendation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-recommendation
-</t>
-  </si>
-  <si>
-    <t>Recommandations</t>
-  </si>
-  <si>
     <t>fr-lm-examination-report.entry.imagingProcedures</t>
   </si>
   <si>
@@ -445,28 +435,6 @@
   </si>
   <si>
     <t>Résultats d'examens</t>
-  </si>
-  <si>
-    <t>fr-lm-examination-report.modality</t>
-  </si>
-  <si>
-    <t>Modalités d'imagerie utilisées lors de l'examen (DICOM CID029)</t>
-  </si>
-  <si>
-    <t>jdv-modalite-acquisition-cisis : Modalité d'imagerie</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-acquisition-cisis</t>
-  </si>
-  <si>
-    <t>fr-lm-examination-report.bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
-</t>
-  </si>
-  <si>
-    <t>Localisations anatomiques</t>
   </si>
 </sst>
 </file>
@@ -768,7 +736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ22"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.953125" customWidth="true" bestFit="true"/>
@@ -795,8 +763,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="40.91015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.5234375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2331,10 +2299,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2406,10 +2374,10 @@
         <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2431,10 +2399,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2506,10 +2474,10 @@
         <v>127</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
@@ -2715,306 +2683,6 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q22" s="2"/>
-      <c r="R22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
         <v>73</v>
       </c>
     </row>
